--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$38</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="76">
   <si>
     <t>Direction</t>
   </si>
@@ -258,12 +258,15 @@
   </si>
   <si>
     <t>10.30.0.18</t>
+  </si>
+  <si>
+    <t>No payment</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ _€"/>
   </numFmts>
@@ -816,8 +819,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF38"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BF39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -1815,6 +1818,10 @@
         <v>54</v>
       </c>
       <c r="L14" s="3"/>
+      <c r="O14" s="38"/>
+      <c r="P14" s="36" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="15" spans="1:58" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -2564,6 +2571,36 @@
       <c r="J38" s="3"/>
       <c r="K38" s="11"/>
       <c r="L38" s="3"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="3">
+        <v>36</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="3">
+        <v>1190237280</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" s="4"/>
+      <c r="I39" s="9">
+        <v>46326</v>
+      </c>
+      <c r="J39" s="3"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="C1:C38"/>
@@ -2575,7 +2612,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF17"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -3213,7 +3250,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -3304,7 +3341,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3525,7 +3562,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -266,7 +266,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0\ _€"/>
   </numFmts>
@@ -820,7 +820,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -2612,7 +2612,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="12.85546875" style="1" customWidth="1"/>
@@ -3250,7 +3250,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
@@ -3341,7 +3341,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>
@@ -3562,7 +3562,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.28515625" customWidth="1"/>
     <col min="3" max="3" width="19.140625" customWidth="1"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$C$38</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -157,9 +157,6 @@
     <t>Tamenrasset</t>
   </si>
   <si>
-    <t>4514+4514Aa</t>
-  </si>
-  <si>
     <t>DAS</t>
   </si>
   <si>
@@ -261,6 +258,9 @@
   </si>
   <si>
     <t>No payment</t>
+  </si>
+  <si>
+    <t>0701+0701Aa</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1343,7 @@
         <v>45557</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L7" s="14" t="s">
         <v>29</v>
@@ -1425,7 +1425,7 @@
         <v>45567</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
@@ -1618,7 +1618,7 @@
         <v>45501</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1"/>
@@ -1700,7 +1700,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="20"/>
       <c r="P12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
@@ -1775,14 +1775,14 @@
         <v>45567</v>
       </c>
       <c r="K13" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>29</v>
       </c>
       <c r="O13" s="21"/>
       <c r="P13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:58" x14ac:dyDescent="0.25">
@@ -1815,12 +1815,12 @@
         <v>45567</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L14" s="3"/>
       <c r="O14" s="38"/>
       <c r="P14" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:58" x14ac:dyDescent="0.25">
@@ -1918,7 +1918,7 @@
         <v>45501</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
@@ -1929,7 +1929,7 @@
         <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D18" s="3">
         <v>847340761</v>
@@ -1952,7 +1952,7 @@
         <v>45540</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
@@ -1963,7 +1963,7 @@
         <v>33</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D19" s="38">
         <v>401804188</v>
@@ -1992,7 +1992,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>8</v>
@@ -2017,7 +2017,7 @@
         <v>45567</v>
       </c>
       <c r="K20" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L20" s="3"/>
     </row>
@@ -2029,7 +2029,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="3">
         <v>1584094343</v>
@@ -2061,7 +2061,7 @@
         <v>33</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D22" s="36">
         <v>1195041370</v>
@@ -2088,7 +2088,7 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>25</v>
@@ -2123,13 +2123,13 @@
         <v>12</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3">
         <v>1640258972</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>16</v>
@@ -2150,7 +2150,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>25</v>
@@ -2204,7 +2204,7 @@
       <c r="J26" s="3"/>
       <c r="K26" s="11"/>
       <c r="L26" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
@@ -2215,7 +2215,7 @@
         <v>12</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D27" s="3">
         <v>1772418636</v>
@@ -2247,10 +2247,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" s="3">
         <v>947448168</v>
@@ -2277,7 +2277,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>5</v>
@@ -2307,10 +2307,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="D30" s="3">
         <v>1124288609</v>
@@ -2346,7 +2346,7 @@
         <v>1702248669</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>16</v>
@@ -2397,7 +2397,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>8</v>
@@ -2430,7 +2430,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D34" s="36">
         <v>1544086645</v>
@@ -2487,7 +2487,7 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>40</v>
@@ -2499,7 +2499,7 @@
         <v>6</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>19</v>
@@ -2517,7 +2517,7 @@
         <v>34</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C37" s="21" t="s">
         <v>38</v>
@@ -2529,7 +2529,7 @@
         <v>9</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G37" s="21" t="s">
         <v>19</v>
@@ -2559,7 +2559,7 @@
         <v>6</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>19</v>
@@ -2589,7 +2589,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>19</v>
@@ -2745,7 +2745,7 @@
         <v>45492</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>35</v>
@@ -2754,10 +2754,10 @@
         <v>36</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="3" spans="1:58" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C3" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="41">
         <v>1605916027</v>
@@ -2814,7 +2814,7 @@
         <v>6</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>19</v>
@@ -3303,7 +3303,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>10</v>
@@ -3326,10 +3326,10 @@
         <v>45487</v>
       </c>
       <c r="K2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -3507,7 +3507,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>10</v>
@@ -3518,7 +3518,7 @@
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16" s="49"/>
       <c r="C16" s="49"/>
@@ -3529,7 +3529,7 @@
     </row>
     <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="49"/>
       <c r="C18" s="49"/>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -3773,7 +3773,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D15" s="25">
         <v>50000</v>
@@ -3787,7 +3787,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" s="25">
         <v>50000</v>
@@ -3798,7 +3798,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>8</v>
@@ -3815,7 +3815,7 @@
         <v>20</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="25">
         <v>50000</v>
@@ -3829,7 +3829,7 @@
         <v>33</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" s="25">
         <v>50000</v>
@@ -3840,7 +3840,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>25</v>
@@ -3857,7 +3857,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="25">
         <v>50000</v>
@@ -3868,7 +3868,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>25</v>
@@ -3914,7 +3914,7 @@
         <v>20</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="26">
         <v>110000</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="49"/>
       <c r="C28" s="49"/>
@@ -3990,7 +3990,7 @@
         <v>1</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>10</v>
@@ -4001,7 +4001,7 @@
     </row>
     <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B42" s="49"/>
       <c r="C42" s="49"/>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="44" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="49" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" s="49"/>
       <c r="C44" s="49"/>
@@ -4022,7 +4022,7 @@
     </row>
     <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="49" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" s="49"/>
       <c r="C46" s="49"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
   <si>
     <t>Direction</t>
   </si>
@@ -819,7 +819,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF39"/>
+  <dimension ref="A1:BF40"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2392,7 +2392,7 @@
       <c r="K32" s="11"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>30</v>
       </c>
@@ -2422,7 +2422,7 @@
       <c r="K33" s="11"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="36">
         <v>31</v>
       </c>
@@ -2452,7 +2452,7 @@
       <c r="K34" s="11"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>32</v>
       </c>
@@ -2482,7 +2482,7 @@
       <c r="K35" s="11"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>33</v>
       </c>
@@ -2512,7 +2512,7 @@
       <c r="K36" s="11"/>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="21">
         <v>34</v>
       </c>
@@ -2542,7 +2542,7 @@
       <c r="K37" s="21"/>
       <c r="L37" s="21"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>35</v>
       </c>
@@ -2572,7 +2572,7 @@
       <c r="K38" s="11"/>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>36</v>
       </c>
@@ -2601,6 +2601,39 @@
       <c r="J39" s="3"/>
       <c r="K39" s="11"/>
       <c r="L39" s="3"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="3">
+        <v>37</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="3">
+        <v>763500236</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" s="4"/>
+      <c r="I40" s="9">
+        <v>46326</v>
+      </c>
+      <c r="J40" s="3"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="1">
+        <v>2027</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="C1:C38"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="78">
   <si>
     <t>Direction</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>0701+0701Aa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SDP </t>
+  </si>
+  <si>
+    <t>DJANET</t>
   </si>
 </sst>
 </file>
@@ -819,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF40"/>
+  <dimension ref="A1:BF41"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2635,6 +2641,14 @@
         <v>2027</v>
       </c>
     </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="C1:C38"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="77">
   <si>
     <t>Direction</t>
   </si>
@@ -261,9 +261,6 @@
   </si>
   <si>
     <t>0701+0701Aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SDP </t>
   </si>
   <si>
     <t>DJANET</t>
@@ -396,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +541,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -825,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BF41"/>
+  <dimension ref="A1:BF42"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="9">
-        <v>46326</v>
+        <v>46691</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="11"/>
@@ -2642,12 +2642,62 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="1" t="s">
+      <c r="A41" s="3">
+        <v>38</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>77</v>
-      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" s="4"/>
+      <c r="I41" s="9">
+        <v>46691</v>
+      </c>
+      <c r="J41" s="3"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="3"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="21">
+        <v>39</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D42" s="21">
+        <v>1168092122</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="22"/>
+      <c r="I42" s="23">
+        <v>46691</v>
+      </c>
+      <c r="J42" s="21"/>
+      <c r="K42" s="50"/>
+      <c r="L42" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="C1:C38"/>

--- a/anydesk.xlsx
+++ b/anydesk.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="2160" windowHeight="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -539,11 +539,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1412,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="3">
-        <v>401172574</v>
+        <v>1711199397</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>9</v>
@@ -1762,7 +1762,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="3">
-        <v>1565013331</v>
+        <v>830828469</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>6</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="29">
-        <v>46326</v>
+        <v>46387</v>
       </c>
       <c r="J13" s="9">
         <v>45567</v>
@@ -2696,7 +2696,7 @@
         <v>46691</v>
       </c>
       <c r="J42" s="21"/>
-      <c r="K42" s="50"/>
+      <c r="K42" s="49"/>
       <c r="L42" s="21"/>
     </row>
   </sheetData>
@@ -3614,32 +3614,32 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
+      <c r="B16" s="50"/>
+      <c r="C16" s="50"/>
       <c r="D16" s="28">
         <f>SUM(D1:D14)</f>
         <v>600000</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A18" s="49" t="s">
+      <c r="A18" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
       <c r="D18" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A20" s="49" t="s">
+      <c r="A20" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="49"/>
+      <c r="B20" s="50"/>
+      <c r="C20" s="50"/>
       <c r="D20" s="28">
         <f>D16-D18</f>
         <v>590000</v>
@@ -4018,11 +4018,11 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A28" s="49" t="s">
+      <c r="A28" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="28">
         <f>D26+D24</f>
         <v>720000</v>
@@ -4097,32 +4097,32 @@
       </c>
     </row>
     <row r="42" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="49" t="s">
+      <c r="A42" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="49"/>
-      <c r="C42" s="49"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="50"/>
       <c r="D42" s="28">
         <f>SUM(D3:D40)</f>
         <v>2100000</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A44" s="49" t="s">
+      <c r="A44" s="50" t="s">
         <v>54</v>
       </c>
-      <c r="B44" s="49"/>
-      <c r="C44" s="49"/>
+      <c r="B44" s="50"/>
+      <c r="C44" s="50"/>
       <c r="D44" s="26">
         <v>10000</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A46" s="49" t="s">
+      <c r="A46" s="50" t="s">
         <v>56</v>
       </c>
-      <c r="B46" s="49"/>
-      <c r="C46" s="49"/>
+      <c r="B46" s="50"/>
+      <c r="C46" s="50"/>
       <c r="D46" s="28">
         <f>D42-D44</f>
         <v>2090000</v>
